--- a/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
+++ b/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
@@ -16,10 +16,10 @@
     <sheet name="Summary" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Completed!$A$1:$E$30</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'New Features (Backlog)'!$A$1:$G$8</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'On Hold'!$A$1:$E$16</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Pending!$A$1:$E$12</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Completed!$A$1:$E$36</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'New Features (Backlog)'!$A$1:$G$9</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'On Hold'!$A$1:$E$15</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Pending!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="237">
   <si>
     <t xml:space="preserve">FlightPro Manager — Master Plan Tracker</t>
   </si>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">How this workbook is organized:</t>
   </si>
   <si>
-    <t xml:space="preserve">  •  Completed — shipped, committed, and (as of 2026-08-25) merged into production.</t>
+    <t xml:space="preserve">  •  Completed — shipped and delivered to the real machine; not every row is committed/merged into production yet (several 2026-08-26 items are delivered-but-uncommitted or committed-to-main-only as of this update) — see the handoff doc for each item's exact git state.</t>
   </si>
   <si>
     <t xml:space="preserve">  •  Pending — code is done and live, but not yet functionally verified. The two Urgent rows are security/accessibility fixes already live on production without having been tested.</t>
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Suggested reading order for a 'what's next' conversation: check Pending first (two Urgent rows are live-on-production-untested and should happen before any new feature work), then compare the New Features sheet's Impact/Effort columns to pick the next build.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: compiled from claude/handoff-2026-08-18.md (the authoritative running log) and claude/next-steps-plan-2026-08-11.md (reconstructed backlog) as of 2026-08-25.</t>
+    <t xml:space="preserve">Source: compiled from the project's handoff doc (the authoritative running log, most recently /home/claude/handoff_work/final.md) as of 2026-08-26.</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -315,6 +315,45 @@
     <t xml:space="preserve">main and production both at commit 4aefc5c, confirmed via real terminal output.</t>
   </si>
   <si>
+    <t xml:space="preserve">Medical Expiry null-input console error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">React "value prop on input should not be null" — fixed missing || '' fallback in lib/store.ts's row mapper and StudentFormModal.tsx's populate-on-edit effect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broader icon-button aria-label coverage (item 38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 files, 19 buttons — Edit/Delete pencil/trash icons across Admin Setup's 7 CRUD tabs plus Availability/Maintenance/Ground School Attendance pages now labeled with the row's own identifying name, not a generic "Edit"/"Delete". Closes the item deliberately deferred from session 7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial Weekly Off Day scheduling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New FTO Settings option covering all 3 real-world patterns: 1 weekly off, 2 weekly offs, or 1 weekly off + occurrence-based (e.g. every 2nd &amp; 4th Saturday, or every 1st/3rd/5th Saturday). Single shared getSchedulingBlockReason() used by every scheduling surface (BookingForm, ScheduleBoard, GroundSchoolCalendar, store).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial Weekly Off Day — Settings save not refreshing shared store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root cause: SettingsTab.tsx wrote settings to Supabase but never refreshed the Zustand store's cached ftoSettings — a pre-existing architectural gap affecting ANY setting change, not just the new feature. Found via user testing (29-08-2026 not blocked), fixed by refreshing the store after save.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA Test Register write access narrowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Removed admin/super_admin from BA_TEST_WRITE_ROLES — only safety_officer + operations can add/edit entries now; admin/super_admin retain view-only access via the existing REPORTS_VIEW_ROLES. Single source of truth (lib/permissions.ts) closes the gap across the UI and all 3 server routes at once.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aircraft Maintenance Schedule — Phase 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New per-model recurring maintenance schedule (engine TBO, Oil Change, 50/100-Hour Inspection, Annual Inspection, Propeller Service, Avionics Check, AD Compliance/ARC review — DGCA-researched, all 5 fleet models) driving: an Aircraft Model dropdown (with "Other" fallback), a non-blocking "Maintenance Due" warning panel, and staff-confirmed Set-Baseline / Create-Maintenance-Record actions. 4 SQL migrations + 13 code files. Phase 2 (hard-blocking bookings on overdue items) deliberately deferred to backlog.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Urgency</t>
   </si>
   <si>
@@ -399,6 +438,24 @@
     <t xml:space="preserve">Dashboard widget / Progress page / Instructor dashboard should all agree, now that the MULTI row exists.</t>
   </si>
   <si>
+    <t xml:space="preserve">Retest Partial Weekly Off Day feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm 29-08-2026 (2nd/4th Saturday rule) is now correctly blocked after the Settings-store-refresh fix — asked but not yet confirmed by the user.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Functionally test BA Test Register permission narrowing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm admin/super_admin can no longer add/edit BA entries (view-only) and safety_officer/operations still can, on the real logged-in app.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Aircraft Maintenance Schedule Phase 1 (IN PROGRESS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 4 SQL migrations run 2026-08-26 — user is currently testing. Confirm: Maintenance Due panel shows the right items per aircraft; Set Baseline / Create Maintenance Record both save correctly; Aircraft Model dropdown populates from the schedule table with "Other" fallback working; logging a completion via the normal Log Maintenance screen (with Hobbs at Completion filled in) resets the matching item's due clock.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Why it's on hold</t>
   </si>
   <si>
@@ -414,15 +471,6 @@
     <t xml:space="preserve">Needs visual verification — not fixable blind in a sandbox with no deployed URL.</t>
   </si>
   <si>
-    <t xml:space="preserve">Broader icon-button aria-label coverage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit/delete pencil/trash icons beyond the Close-button scope already fixed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scoped out of session 7 to the most acute gap (Close buttons) first.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Two more unhardened write paths</t>
   </si>
   <si>
@@ -639,6 +687,15 @@
     <t xml:space="preserve">No user demand signal yet beyond the original backlog line item — lowest apparent priority of the five backlog items.</t>
   </si>
   <si>
+    <t xml:space="preserve">Aircraft Maintenance Schedule — Phase 2 (hard-block bookings)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-ground / block scheduling when a mandatory maintenance item goes overdue, instead of Phase 1's non-blocking warnings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliberately deferred by the user's own request until Phase 1 is confirmed working in practice; needs a decision on which items (if any) should be hard-blocking vs. warning-only, and how a false-positive baseline would be handled before an aircraft gets auto-grounded.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Plan Tracker — Summary</t>
   </si>
   <si>
@@ -663,22 +720,28 @@
     <t xml:space="preserve">Suggested next steps, in order</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Run the two Urgent items in Pending — session 7's security + accessibility fixes are live on production, untested. This is risk reduction, not new work, and should come first regardless of what's picked next.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Clear the rest of Pending with a normal testing pass (see the Pre-Handover Test Plan for the detailed step-by-step cases).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. For new feature work: Checkbox-style Requirements UI is the smallest, most self-contained backlog item and was already flagged as the natural next step — good first pick if you want visible progress fast.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. The two DGCA implementation items (Incident Report, Maintenance Log) are High impact but blocked on you verifying the draft templates against the FTO's real paperwork first — worth doing that verification soon so they're unblocked whenever there's room.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Billing and Multi-FTO are both High-impact but Large-effort with no scoping done yet — good candidates for a dedicated scoping conversation before committing to either.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Mobile PWA installability and Multi-language are lower urgency — park until something above them is done.</t>
+    <t xml:space="preserve">1. Run the two Urgent items in Pending — session 7's security + accessibility fixes are live on production, still untested as of this update. This is risk reduction, not new work, and should come first regardless of what's picked next.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Finish testing the Aircraft Maintenance Schedule Phase 1 — all 4 SQL migrations are run, user is actively testing as of 2026-08-26 (see Pending). Once confirmed working, commit/push/merge and consider scoping Phase 2 (hard-blocking).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Retest Partial Weekly Off Day (29-08-2026 case) and functionally verify the BA Test Register permission narrowing — both shipped fixes awaiting confirmation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Clear the rest of Pending with a normal testing pass (see the Pre-Handover Test Plan for the detailed step-by-step cases).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. For new feature work: Checkbox-style Requirements UI is still the smallest, most self-contained backlog item — good first pick if you want visible progress fast once the above testing is clear.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. The two DGCA implementation items (Incident Report, Maintenance Log) are High impact but blocked on you verifying the draft templates against the FTO's real paperwork first — worth doing that verification soon so they're unblocked whenever there's room.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Billing and Multi-FTO are both High/Medium-impact but Large-effort with no scoping done yet — good candidates for a dedicated scoping conversation before committing to either.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. Mobile PWA installability, Multi-language, and Aircraft Maintenance Schedule Phase 2 are lower urgency — park until something above them is done.</t>
   </si>
 </sst>
 </file>
@@ -879,8 +942,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -936,11 +1003,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -948,16 +1015,20 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1296,56 +1367,56 @@
   <dimension ref="A1:A14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="105"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="105"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1365,528 +1436,630 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="n">
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="n">
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="n">
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="n">
+    <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="n">
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="n">
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="n">
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="n">
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="n">
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="n">
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="n">
+    <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="6" t="s">
         <v>77</v>
       </c>
     </row>
+    <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E30"/>
+  <autoFilter ref="A1:E36"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1903,222 +2076,273 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="n">
+      <c r="E1" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+      <c r="C2" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="C3" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="C4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+      <c r="B5" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+      <c r="B6" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+      <c r="B7" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="B8" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+      <c r="B9" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+      <c r="B10" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
+      <c r="C11" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>109</v>
+      <c r="B12" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E12"/>
+  <autoFilter ref="A1:E15"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2138,287 +2362,271 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="n">
+      <c r="E1" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="n">
+      <c r="B2" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="n">
+      <c r="B3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="n">
+      <c r="B4" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="n">
+      <c r="B5" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="n">
+      <c r="B6" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="n">
+      <c r="B7" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="n">
+      <c r="B8" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="n">
+      <c r="B9" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="n">
+      <c r="B10" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="n">
+      <c r="C11" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="n">
+      <c r="B12" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>169</v>
-      </c>
-    </row>
+      <c r="C15" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:E16"/>
+  <autoFilter ref="A1:E15"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2435,203 +2643,226 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="n">
+      <c r="C1" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+      <c r="B2" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="B3" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="B4" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+      <c r="B5" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="B6" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="E6" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>201</v>
+      <c r="E9" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G9"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2648,127 +2879,137 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="14" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="B3" s="16" t="n">
-        <f aca="false">29</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="B4" s="16" t="n">
-        <f aca="false">11</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" s="16" t="n">
-        <f aca="false">COUNTIF(Pending!E2:E12,"Urgent")</f>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="17" t="n">
+        <f aca="false">COUNT(Completed!A:A)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="17" t="n">
+        <f aca="false">COUNT(Pending!A:A)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="17" t="n">
+        <f aca="false">COUNTIF(Pending!E:E,"Urgent")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="16" t="n">
-        <f aca="false">15</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="B7" s="16" t="n">
-        <f aca="false">7</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIF('New Features (Backlog)'!E2:E8,"High")</f>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" s="17" t="n">
+        <f aca="false">COUNT('On Hold'!A:A)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="17" t="n">
+        <f aca="false">COUNT('New Features (Backlog)'!A:A)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="17" t="n">
+        <f aca="false">COUNTIF('New Features (Backlog)'!E:E,"High")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
+      <c r="A11" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
+      <c r="A12" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
+      <c r="A13" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
+      <c r="A14" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="A15" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
+      <c r="A16" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
+        <v>236</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
+++ b/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="259">
   <si>
     <t xml:space="preserve">FlightPro Manager — Master Plan Tracker</t>
   </si>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">How this workbook is organized:</t>
   </si>
   <si>
-    <t xml:space="preserve">  •  Completed — shipped and delivered to the real machine; not every row is committed/merged into production yet (several 2026-08-26 items are delivered-but-uncommitted or committed-to-main-only as of this update) — see the handoff doc for each item's exact git state.</t>
+    <t xml:space="preserve">  •  Completed — shipped and delivered to the real machine; the great majority is now committed, pushed, and merged into production — see the handoff doc for each item's exact git state.</t>
   </si>
   <si>
     <t xml:space="preserve">  •  Pending — code is done and live, but not yet functionally verified. The two Urgent rows are security/accessibility fixes already live on production without having been tested.</t>
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Suggested reading order for a 'what's next' conversation: check Pending first (two Urgent rows are live-on-production-untested and should happen before any new feature work), then compare the New Features sheet's Impact/Effort columns to pick the next build.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: compiled from the project's handoff doc (the authoritative running log, most recently /home/claude/handoff_work/final.md) as of 2026-08-26.</t>
+    <t xml:space="preserve">Source: compiled from the project's handoff doc (the authoritative running log, most recently claude/handoff-2026-08-27.md) as of 2026-08-27.</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -354,6 +354,48 @@
     <t xml:space="preserve">New per-model recurring maintenance schedule (engine TBO, Oil Change, 50/100-Hour Inspection, Annual Inspection, Propeller Service, Avionics Check, AD Compliance/ARC review — DGCA-researched, all 5 fleet models) driving: an Aircraft Model dropdown (with "Other" fallback), a non-blocking "Maintenance Due" warning panel, and staff-confirmed Set-Baseline / Create-Maintenance-Record actions. 4 SQL migrations + 13 code files. Phase 2 (hard-blocking bookings on overdue items) deliberately deferred to backlog.</t>
   </si>
   <si>
+    <t xml:space="preserve">Aircraft Maintenance Schedule — Type/Model engine-type filtering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model dropdown now filtered by the selected engine Type (Single/Multi Engine); switching Type clears a now-mismatched Model. A model not yet mapped is shown for either Type so nothing becomes unselectable by omission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aircraft Maintenance Schedule — fleet expansion to 9 models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added Cessna 152, Piper PA-28 Cherokee/Archer, Piper Archer DX, and Diamond DA40 with DGCA/manufacturer-researched schedule data (real sources, same discipline as the original 5 models).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type/Model engine-type mapping moved from hardcoded to DB-driven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New engine_type column on the schedule-template table, with an Admin Setup selector; adding or changing a model's engine type no longer needs a code change/redeploy — closes the last hardcoded-list gap in this feature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aircraft Maintenance Schedule Phase 1 + fleet expansion committed, pushed, and merged into production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two commits (b1a5bd8, 819baef), both independently verified against GitHub. Merged to production before all testing was complete, per the user's explicit informed call.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UX / Data integrity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aircraft Model "Other (custom)" now warns and blocks Save instead of accepting free text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User's own suggestion: a custom Model that doesn't match a schedule template silently broke Maintenance Due tracking (the exact bug found earlier). Picking "Other" in both AircraftFormModal.tsx and AircraftSetupTab.tsx now shows an inline warning naming the current value (if any) and disables Save, pointing the admin at Admin Setup &gt; Aircraft Maintenance Schedule; a "Refresh list" button lets them pick the newly-added model without closing the form. Free text is kept ONLY as a bootstrap fallback for the (currently hypothetical) case of an empty schedule-template table. tsc clean, eslint introduces zero new issues (verified against the pre-edit baseline). Delivered to the real machine, confirmed byte-for-byte — not yet committed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aircraft Maintenance Schedule — CSV bulk import (Download Template / Upload CSV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User's request: adding schedule items one at a time was too slow for onboarding a new aircraft type's whole schedule. Added a Download Template / Upload CSV pair to the Admin Setup tab, mirroring ExercisesTab.tsx's existing CSV pattern (same papaparse library, same Append + skip-duplicates rule, no new dependency). Reuses the existing secured bulk-insert path in /api/admin/config/[table]/route.ts (already supported an array body) — no API changes needed. CSV rows can span multiple aircraft models in one upload, not just the currently-selected one. Client-side validates interval_type, interval_value, and engine_type before submitting (the DB CHECK constraints would otherwise fail the WHOLE batch on one bad row, since it's a single insert call) and pre-dedupes against the table's own unique(aircraft_model, item_name) constraint. tsc clean; eslint confirmed zero new issues via before/after diff against the unedited baseline. Delivered to the real machine, confirmed byte-for-byte — not yet committed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Urgency</t>
   </si>
   <si>
@@ -453,7 +495,19 @@
     <t xml:space="preserve">Test Aircraft Maintenance Schedule Phase 1 (IN PROGRESS)</t>
   </si>
   <si>
-    <t xml:space="preserve">All 4 SQL migrations run 2026-08-26 — user is currently testing. Confirm: Maintenance Due panel shows the right items per aircraft; Set Baseline / Create Maintenance Record both save correctly; Aircraft Model dropdown populates from the schedule table with "Other" fallback working; logging a completion via the normal Log Maintenance screen (with Hobbs at Completion filled in) resets the matching item's due clock.</t>
+    <t xml:space="preserve">Confirmed working: Admin Setup schedule tab (9 models, Engine Type selector), Add/Edit Aircraft Type/Model filtering (incl. "Other (custom)" fallback and the pre-existing-aircraft Model re-pick), and the Maintenance Due panel's own Set Baseline / Create Maintenance Record buttons. Still needs a deliberate test: logging a completion through the normal "Log Maintenance" screen (not the Due panel's own buttons) — Type = Oil Change or similar, Status = Completed, Hobbs at Completion filled in — confirm the matching Due-panel item resets. This is the exact path the earlier item-name-mismatch bug was found and fixed in, so worth exercising deliberately rather than assuming it still works.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General regression pass over the rest of the app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Booking, Flight Records, Ground School, and the other Admin Setup tabs — nothing in this session's Aircraft Maintenance Schedule work should have touched them, but worth a normal-use sanity check now that everything (schedule feature, Type/Model filtering, fleet expansion, DB-driven engine type) is live on production.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test "Other (custom)" Model warn-and-block behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add/Edit Aircraft, both AircraftFormModal.tsx and the Admin Setup Aircraft tab: pick "Other (custom)…", confirm the warning shows and Save/Add is disabled; add the model via Admin Setup &gt; Aircraft Maintenance Schedule, click "Refresh list", confirm it now appears and can be picked and saved. Also edit an aircraft with a legacy unmatched Model and confirm the same warning/block appears until it's re-picked.</t>
   </si>
   <si>
     <t xml:space="preserve">Why it's on hold</t>
@@ -696,6 +750,18 @@
     <t xml:space="preserve">Deliberately deferred by the user's own request until Phase 1 is confirmed working in practice; needs a decision on which items (if any) should be hard-blocking vs. warning-only, and how a false-positive baseline would be handled before an aircraft gets auto-grounded.</t>
   </si>
   <si>
+    <t xml:space="preserve">One-time "unrecognized Model" admin banner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A banner/flag (e.g. on Admin Setup or the Aircraft list) when N aircraft have a Model value that doesn't match any maintenance schedule template, with a one-click path to the affected aircraft's Edit form to re-pick the correct Model from the dropdown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27 update: new aircraft can no longer be created/saved with an unrecognized Model at all (see Completed) — this item now only covers EXISTING aircraft that predate that fix (or were saved before the DB-driven engine_type migration). Lower priority than originally scoped, since the main failure mode is now closed at the point of entry.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Plan Tracker — Summary</t>
   </si>
   <si>
@@ -723,7 +789,7 @@
     <t xml:space="preserve">1. Run the two Urgent items in Pending — session 7's security + accessibility fixes are live on production, still untested as of this update. This is risk reduction, not new work, and should come first regardless of what's picked next.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Finish testing the Aircraft Maintenance Schedule Phase 1 — all 4 SQL migrations are run, user is actively testing as of 2026-08-26 (see Pending). Once confirmed working, commit/push/merge and consider scoping Phase 2 (hard-blocking).</t>
+    <t xml:space="preserve">2. Aircraft Maintenance Schedule Phase 1 + fleet expansion are now committed, pushed, and merged into production (2026-08-27). One targeted test remains — logging a completion via the normal Log Maintenance screen with Hobbs at Completion — plus a general regression pass over the rest of the app (see Pending). Once clear, consider scoping Phase 2 (hard-blocking bookings).</t>
   </si>
   <si>
     <t xml:space="preserve">3. Retest Partial Weekly Off Day (29-08-2026 case) and functionally verify the BA Test Register permission narrowing — both shipped fixes awaiting confirmation.</t>
@@ -1436,7 +1502,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -2056,6 +2122,108 @@
       </c>
       <c r="E36" s="6" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2076,7 +2244,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -2100,7 +2268,7 @@
         <v>13</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2111,13 +2279,13 @@
         <v>15</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2128,13 +2296,13 @@
         <v>25</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2145,13 +2313,13 @@
         <v>81</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2159,16 +2327,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2176,16 +2344,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2193,16 +2361,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2210,16 +2378,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2227,16 +2395,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2244,16 +2412,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2261,16 +2429,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2278,16 +2446,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2295,16 +2463,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D13" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>136</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2312,16 +2480,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2329,16 +2497,50 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>122</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2383,7 +2585,7 @@
         <v>13</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2391,16 +2593,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2411,13 +2613,13 @@
         <v>15</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2425,16 +2627,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2442,16 +2644,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2459,16 +2661,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2476,16 +2678,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2493,16 +2695,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2510,16 +2712,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2527,16 +2729,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2544,16 +2746,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2561,16 +2763,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2578,16 +2780,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2595,16 +2797,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2612,16 +2814,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2643,7 +2845,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -2662,19 +2864,19 @@
         <v>30</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2682,22 +2884,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2705,22 +2907,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2728,22 +2930,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2751,22 +2953,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2774,22 +2976,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2797,22 +2999,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="E7" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>194</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2820,22 +3022,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2843,22 +3045,45 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>220</v>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -2888,30 +3113,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="B3" s="17" t="n">
         <f aca="false">COUNT(Completed!A:A)</f>
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">COUNT(Pending!A:A)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">COUNTIF(Pending!E:E,"Urgent")</f>
@@ -2920,7 +3145,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">COUNT('On Hold'!A:A)</f>
@@ -2929,16 +3154,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">COUNT('New Features (Backlog)'!A:A)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">COUNTIF('New Features (Backlog)'!E:E,"High")</f>
@@ -2947,7 +3172,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -2955,7 +3180,7 @@
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -2963,7 +3188,7 @@
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -2971,7 +3196,7 @@
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -2979,7 +3204,7 @@
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -2987,7 +3212,7 @@
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -2995,7 +3220,7 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -3003,12 +3228,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
+++ b/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="262">
   <si>
     <t xml:space="preserve">FlightPro Manager — Master Plan Tracker</t>
   </si>
@@ -387,33 +387,45 @@
     <t xml:space="preserve">Aircraft Model "Other (custom)" now warns and blocks Save instead of accepting free text</t>
   </si>
   <si>
-    <t xml:space="preserve">User's own suggestion: a custom Model that doesn't match a schedule template silently broke Maintenance Due tracking (the exact bug found earlier). Picking "Other" in both AircraftFormModal.tsx and AircraftSetupTab.tsx now shows an inline warning naming the current value (if any) and disables Save, pointing the admin at Admin Setup &gt; Aircraft Maintenance Schedule; a "Refresh list" button lets them pick the newly-added model without closing the form. Free text is kept ONLY as a bootstrap fallback for the (currently hypothetical) case of an empty schedule-template table. tsc clean, eslint introduces zero new issues (verified against the pre-edit baseline). Delivered to the real machine, confirmed byte-for-byte — not yet committed.</t>
+    <t xml:space="preserve">User's own suggestion: a custom Model that doesn't match a schedule template silently broke Maintenance Due tracking (the exact bug found earlier). Picking "Other" in both AircraftFormModal.tsx and AircraftSetupTab.tsx now shows an inline warning naming the current value (if any) and disables Save, pointing the admin at Admin Setup &gt; Aircraft Maintenance Schedule; a "Refresh list" button lets them pick the newly-added model without closing the form. Free text is kept ONLY as a bootstrap fallback for the (currently hypothetical) case of an empty schedule-template table. tsc clean, eslint introduces zero new issues (verified against the pre-edit baseline). Committed, pushed, and merged into production same day (commit e137913) — independently verified via git ls-remote: both main and production resolve to e1379130022e31a028f0d83ae4a6623c9f86d424.</t>
   </si>
   <si>
     <t xml:space="preserve">Aircraft Maintenance Schedule — CSV bulk import (Download Template / Upload CSV)</t>
   </si>
   <si>
-    <t xml:space="preserve">User's request: adding schedule items one at a time was too slow for onboarding a new aircraft type's whole schedule. Added a Download Template / Upload CSV pair to the Admin Setup tab, mirroring ExercisesTab.tsx's existing CSV pattern (same papaparse library, same Append + skip-duplicates rule, no new dependency). Reuses the existing secured bulk-insert path in /api/admin/config/[table]/route.ts (already supported an array body) — no API changes needed. CSV rows can span multiple aircraft models in one upload, not just the currently-selected one. Client-side validates interval_type, interval_value, and engine_type before submitting (the DB CHECK constraints would otherwise fail the WHOLE batch on one bad row, since it's a single insert call) and pre-dedupes against the table's own unique(aircraft_model, item_name) constraint. tsc clean; eslint confirmed zero new issues via before/after diff against the unedited baseline. Delivered to the real machine, confirmed byte-for-byte — not yet committed.</t>
+    <t xml:space="preserve">User's request: adding schedule items one at a time was too slow for onboarding a new aircraft type's whole schedule. Added a Download Template / Upload CSV pair to the Admin Setup tab, mirroring ExercisesTab.tsx's existing CSV pattern (same papaparse library, same Append + skip-duplicates rule, no new dependency). Reuses the existing secured bulk-insert path in /api/admin/config/[table]/route.ts (already supported an array body) — no API changes needed. CSV rows can span multiple aircraft models in one upload, not just the currently-selected one. Client-side validates interval_type, interval_value, and engine_type before submitting (the DB CHECK constraints would otherwise fail the WHOLE batch on one bad row, since it's a single insert call) and pre-dedupes against the table's own unique(aircraft_model, item_name) constraint. tsc clean; eslint confirmed zero new issues via before/after diff against the unedited baseline. Committed, pushed, and merged into production same day (commit e137913) — independently verified via git ls-remote: both main and production resolve to e1379130022e31a028f0d83ae4a6623c9f86d424.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test security-hardening round (automated portion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21 security-hardening round (Admin Setup config-CRUD, Aircraft routes, Direct Exam Entry role gating) verified against LIVE PRODUCTION on 2026-08-28 via an automated Node.js script (scripts/security-hardening-test.mjs) covering all 7 test accounts (super_admin/admin/operations/maintenance/instructor/safety_officer/student): 114/114 automated checks passed, 0 failed. Every non-super_admin role correctly rejected (403) on all 8 Admin Setup config tables (POST tested per table; PATCH/DELETE role gating spot-checked on exercises as the representative table, since every table shares the identical one-line requireRole() check); a non-whitelisted body field was confirmed dropped rather than persisted. Aircraft routes correctly allow only admin/super_admin and reject every other role on POST/PATCH/DELETE. Direct Exam Entry correctly rejects every non-admin/instructor/super_admin role. All throwaway test rows self-cleaned with zero leftovers. Full report: scripts/security-test-reports/security-test-2026-08-28T08-24-16-652Z.{txt,html,json}. NOT covered by this automated pass (tracked separately in Pending): the Ground School Progress IDOR fix (client-side-only, needs a manual browser check with a second student account) and Direct Exam Entry's positive/allowed-role path (no safe automated cleanup path).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28 (session 7 cont.)</t>
   </si>
   <si>
     <t xml:space="preserve">Urgency</t>
   </si>
   <si>
-    <t xml:space="preserve">Test security-hardening round</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All 7 Admin Setup config-route tabs, Aircraft Setup, the IDOR fix, and the direct-exam-entry route — live on production, untested.</t>
+    <t xml:space="preserve">Manually verify remaining security-hardening items (IDOR + direct-exam positive path)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated round (all 8 Admin Setup config tables, Aircraft Setup, Direct Exam Entry negative path) passed 114/114 against production on 2026-08-28 — see Completed and scripts/security-test-reports/. Two items still need manual verification because they can't be safely automated: (1) the Ground School Progress IDOR fix (?student= URL override) — a client-side React guard with no server-observable difference, needs a real browser click-through with two distinct student accounts (only one dummy student account has been provided so far — a second is needed to actually exercise this); (2) the Direct Exam Entry route's positive/allowed-role path — no DELETE endpoint and no FK-existence check on the insert, so a successful call can't be cleanly undone; verify manually and clean up the resulting ground_school_enrollment row by hand if exercised.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test accessibility-hardening round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escape closes all 15 modals; all 11 Close buttons announce correctly to a screen reader — live on production, untested.</t>
   </si>
   <si>
     <t xml:space="preserve">Urgent</t>
   </si>
   <si>
-    <t xml:space="preserve">Test accessibility-hardening round</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escape closes all 15 modals; all 11 Close buttons announce correctly to a screen reader — live on production, untested.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Test My Students instructor-only scoping</t>
   </si>
   <si>
@@ -441,9 +453,6 @@
     <t xml:space="preserve">Training-stage dropdown, student cards, students-list filter, target-hours consistency, Multi Engine/Simulator progress cards, Breath Analyser Register + Report end-to-end, instructor CPL server-side block, SPL/CPL issue-date fields.</t>
   </si>
   <si>
-    <t xml:space="preserve">Normal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Permission override feature — no live test yet</t>
   </si>
   <si>
@@ -507,7 +516,7 @@
     <t xml:space="preserve">Test "Other (custom)" Model warn-and-block behavior</t>
   </si>
   <si>
-    <t xml:space="preserve">Add/Edit Aircraft, both AircraftFormModal.tsx and the Admin Setup Aircraft tab: pick "Other (custom)…", confirm the warning shows and Save/Add is disabled; add the model via Admin Setup &gt; Aircraft Maintenance Schedule, click "Refresh list", confirm it now appears and can be picked and saved. Also edit an aircraft with a legacy unmatched Model and confirm the same warning/block appears until it's re-picked.</t>
+    <t xml:space="preserve">LIVE ON PRODUCTION as of 2026-08-27 (commit e137913), untested. Add/Edit Aircraft, both AircraftFormModal.tsx and the Admin Setup Aircraft tab: pick "Other (custom)…", confirm the warning shows and Save/Add is disabled; add the model via Admin Setup &gt; Aircraft Maintenance Schedule, click "Refresh list", confirm it now appears and can be picked and saved. Also edit an aircraft with a legacy unmatched Model and confirm the same warning/block appears until it's re-picked.</t>
   </si>
   <si>
     <t xml:space="preserve">Why it's on hold</t>
@@ -786,7 +795,7 @@
     <t xml:space="preserve">Suggested next steps, in order</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Run the two Urgent items in Pending — session 7's security + accessibility fixes are live on production, still untested as of this update. This is risk reduction, not new work, and should come first regardless of what's picked next.</t>
+    <t xml:space="preserve">1. Accessibility testing (session 7's fixes are live on production, still untested) is now the one remaining Urgent item — run it next. Security's automated round passed 114/114 against production on 2026-08-28; only two narrow manual-only checks are left there (see Pending), no longer blocking.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Aircraft Maintenance Schedule Phase 1 + fleet expansion are now committed, pushed, and merged into production (2026-08-27). One targeted test remains — logging a completion via the normal Log Maintenance screen with Hobbs at Completion — plus a general regression pass over the rest of the app (see Pending). Once clear, consider scoping Phase 2 (hard-blocking bookings).</t>
@@ -1502,7 +1511,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -2224,6 +2233,23 @@
       </c>
       <c r="E42" s="6" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2268,7 +2294,7 @@
         <v>13</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2279,13 +2305,13 @@
         <v>15</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2296,13 +2322,13 @@
         <v>25</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2313,13 +2339,13 @@
         <v>81</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2327,16 +2353,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2344,16 +2370,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2361,16 +2387,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2378,16 +2404,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2395,16 +2421,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2412,16 +2438,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2429,16 +2455,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2446,16 +2472,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2463,16 +2489,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2480,16 +2506,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2497,16 +2523,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2514,16 +2540,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2531,16 +2557,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>133</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2585,7 +2611,7 @@
         <v>13</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2593,16 +2619,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2613,13 +2639,13 @@
         <v>15</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2627,16 +2653,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2644,16 +2670,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2661,16 +2687,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2678,16 +2704,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2695,16 +2721,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2712,16 +2738,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2729,16 +2755,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2746,16 +2772,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2763,16 +2789,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2780,16 +2806,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2797,16 +2823,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2814,16 +2840,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2864,19 +2890,19 @@
         <v>30</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2884,22 +2910,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2907,22 +2933,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>212</v>
-      </c>
       <c r="G3" s="8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2930,22 +2956,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>216</v>
-      </c>
       <c r="E4" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2953,22 +2979,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2976,22 +3002,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2999,22 +3025,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>227</v>
-      </c>
       <c r="G7" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3022,22 +3048,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3045,22 +3071,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3068,22 +3094,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -3113,21 +3139,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B3" s="17" t="n">
         <f aca="false">COUNT(Completed!A:A)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">COUNT(Pending!A:A)</f>
@@ -3136,16 +3162,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">COUNTIF(Pending!E:E,"Urgent")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">COUNT('On Hold'!A:A)</f>
@@ -3154,7 +3180,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">COUNT('New Features (Backlog)'!A:A)</f>
@@ -3163,7 +3189,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">COUNTIF('New Features (Backlog)'!E:E,"High")</f>
@@ -3172,7 +3198,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3180,7 +3206,7 @@
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -3188,7 +3214,7 @@
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -3196,7 +3222,7 @@
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -3204,7 +3230,7 @@
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -3212,7 +3238,7 @@
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -3220,7 +3246,7 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -3228,12 +3254,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
+++ b/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
@@ -664,7 +664,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="39" customHeight="1" s="23">
       <c r="A3" s="25" t="inlineStr">
         <is>
@@ -672,7 +671,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="23">
       <c r="A5" s="26" t="inlineStr">
         <is>
@@ -715,7 +713,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="39" customHeight="1" s="23">
       <c r="A12" s="26" t="inlineStr">
         <is>
@@ -723,7 +720,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="26.25" customHeight="1" s="23">
       <c r="A14" s="25" t="inlineStr">
         <is>
@@ -744,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="22" min="1" max="1"/>
@@ -2479,7 +2475,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" s="23">
       <c r="A68" s="28" t="inlineStr">
         <is>
           <t>67</t>
@@ -2503,6 +2499,141 @@
       <c r="E68" s="28" t="inlineStr">
         <is>
           <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" s="23">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69" s="28" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>Quick-reschedule buttons left a stale OVERDUE state (09-05 open-items list, item 66)</t>
+        </is>
+      </c>
+      <c r="D69" s="28" t="inlineStr">
+        <is>
+          <t>ROOT CAUSE FOUND. updateMaintenanceRecord() spliced the PATCH body into the SWR cache with {revalidate:false}. isOverdue and daysUntilDue are DERIVED in fetchMaintenanceRecords from maintenanceEnd/scheduledDate/status, so the splice copied the new end time but left the derived fields at their fetch-time values: the window text moved, the red row and OVERDUE badge did not. Same bug hit Complete (a completed record kept its overdue styling). Fixed by revalidating instead of recomputing the derivation in a second place. VERIFIED LIVE 2026-09-11 on a throwaway record (since deleted): +4h moved 11:00-&gt;15:00 and correctly stayed OVERDUE (still past); two +1d clicks pushed the end 40 min into the future and the badge and red row cleared with no refresh. NOTE: the buttons only render when a record has a maintenanceEnd — none of the current live records do, so on production data they are invisible, which may be part of the original report.</t>
+        </is>
+      </c>
+      <c r="E69" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" s="23">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70" s="28" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>Consolidated DGCA audit-pack export</t>
+        </is>
+      </c>
+      <c r="D70" s="28" t="inlineStr">
+        <is>
+          <t>One PDF for a date range: every saved Daily Flying Report, the BA register rollup, and the Maintenance Log per aircraft with completed work. New page /dashboard/reports/audit-pack + card on the Reports landing page. lib/pdf.ts: the four existing generators each take an optional trailing doc and return it (section()/finish() helpers), so a section appends as new pages instead of downloading separately; the four existing call sites are unchanged. Orientation is per-page, so the landscape Maintenance Log coexists with the portrait reports. generateBreathAnalysisReport's period union gained 'Custom' — labelling an arbitrary range 'Monthly' on a regulator-facing page would be false. Missing days are NOT auto-generated (that would write saved reports as a side effect of an export) — they are listed on screen and printed on the cover. Range capped at 92 days. VERIFIED LIVE 2026-09-11: 4-page pack, cover counts matched an independent data query, all 30 gap dates printed, orientation correct, both range guards working, no app-side console or network errors.</t>
+        </is>
+      </c>
+      <c r="E70" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" s="23">
+      <c r="A71" s="28" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71" s="28" t="inlineStr">
+        <is>
+          <t>Feature gap</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>Maintenance Log header — Log Book Serial No. and CAMO/AMO Approval No.</t>
+        </is>
+      </c>
+      <c r="D71" s="28" t="inlineStr">
+        <is>
+          <t>MOVED FROM PENDING (was row 21) — shipped 2026-09-10 in commit 6858b33 and never moved out of Pending. aircraft.log_book_serial_no + fto_settings key camo_approval_no, migration add-logbook-and-camo-refs.sql (applied). Both are UNVALIDATED PLACEHOLDERS: the report omits the whole header line when they are blank rather than printing an empty label. Still blocked on a real log book cover page and a real CAMO/AMO approval certificate; expected change is labels only, not storage.</t>
+        </is>
+      </c>
+      <c r="E71" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-10 (6858b33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" s="23">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72" s="28" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C72" s="29" t="inlineStr">
+        <is>
+          <t>Cron job silent-failure fallback to anon key</t>
+        </is>
+      </c>
+      <c r="D72" s="28" t="inlineStr">
+        <is>
+          <t>MOVED FROM ON HOLD (was row 11) — closed 2026-09-10 in commit b55797a and never moved. lib/supabase-admin.ts no longer falls back to the anon key when SUPABASE_SERVICE_KEY is missing; the old behaviour returned 200 with RLS-filtered (usually empty) data instead of failing. Deliberately still does not throw at module load, because next build imports these modules and a build-time env gap would fail the deploy.</t>
+        </is>
+      </c>
+      <c r="E72" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-10 (b55797a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73" s="28" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C73" s="29" t="inlineStr">
+        <is>
+          <t>Projected finish from actual flying rate (progression, phase 1)</t>
+        </is>
+      </c>
+      <c r="D73" s="28" t="inlineStr">
+        <is>
+          <t>lib/training-pace.ts + lib/training-pace.test.ts, shown as one line under the Progress page metric cards. Projects time-to-target from hours flown in a trailing 56-day window. CORRECTS A WRONG PREMISE: the comparison doc called pace-vs-target 'a computed view over data we already have'. It is not — training_programs has NO course duration and students.joinedDate is optional and null on every current row, so there is no required pace to compare against. This measures what the data does support. Returns null when no total-hours target is configured (same convention as requirementPercent). Reports sample size with every rate so 2 flights are not read as a trend; caps at 2 years and suppresses the date rather than projecting into the 2040s; a student who flew then stopped reads as STALLED with their last flight date, which is the case worth acting on. VERIFIED LIVE 2026-09-11: Dummy Student (3h of 200h, 2 flights) rendered '0.4h/week — over 2 years to target at this rate (2 flights in 8w)' — the far-off guard firing on real data; Dummy Student Two rendered 'No flights recorded yet'. tsx test, tsc and lint all clean.</t>
+        </is>
+      </c>
+      <c r="E73" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="22" min="1" max="1"/>
@@ -2598,7 +2729,7 @@
       </c>
       <c r="D3" s="30" t="inlineStr">
         <is>
-          <t>Escape closes all 15 modals; all 11 Close buttons announce correctly to a screen reader — live on production since session 7, STILL UNTESTED as of 2026-09-10. This has been the only Urgent row for two weeks.</t>
+          <t>PARTIALLY VERIFIED 2026-09-11: Escape confirmed closing the Maintenance edit modal in a real browser, and the ConfirmDialog/stack fix shipped 2026-09-10 (4964989). STILL OPEN: the other 14 modals, and NO SCREEN READER HAS BEEN RUN — accessible names were verified in the accessibility tree only. The original tracker claim ('Escape closes all 15 modals; all 11 Close buttons announce correctly to a screen reader') was false on both halves; do not re-tick this row on tree inspection alone.</t>
         </is>
       </c>
       <c r="E3" s="32" t="inlineStr">
@@ -3062,33 +3193,6 @@
       <c r="E21" s="33" t="inlineStr">
         <is>
           <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B22" s="30" t="inlineStr">
-        <is>
-          <t>Feature gap</t>
-        </is>
-      </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>Maintenance Log header — Log Book Serial No. and CAMO/AMO Approval No.</t>
-        </is>
-      </c>
-      <c r="D22" s="30" t="inlineStr">
-        <is>
-          <t>Both appear on the draft template's aircraft-details block and exist nowhere in the schema. Needs a column on aircraft and an fto_settings key. ~30 min, and it closes a visible gap in something already shipped — but confirm the field names against the real register first.</t>
-        </is>
-      </c>
-      <c r="E22" s="33" t="inlineStr">
-        <is>
-          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="22" min="1" max="1"/>
@@ -3395,7 +3499,7 @@
     </row>
     <row r="12" ht="23.25" customHeight="1" s="23">
       <c r="A12" s="35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
@@ -3404,99 +3508,101 @@
       </c>
       <c r="C12" s="36" t="inlineStr">
         <is>
-          <t>Cron job silent-failure fallback to anon key</t>
+          <t>Optional: backfill expiry/issue dates</t>
         </is>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>check-notifications/route.ts may silently fall back to the anon key if the service-role key is unset (flow audit finding #8).</t>
+          <t>Existing SPL/CPL numbers on file have no expiry/issue date backfilled.</t>
         </is>
       </c>
       <c r="E12" s="35" t="inlineStr">
         <is>
-          <t>Never confirmed fixed or broken — WORST STATE FOR A SECURITY ITEM. Worth five minutes next time that file is touched; it has now been open since the flow audit.</t>
+          <t>Optional, no user request yet.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" s="23">
       <c r="A13" s="35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Cosmetic</t>
         </is>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>Optional: backfill expiry/issue dates</t>
+          <t>Minor pre-existing inconsistencies</t>
         </is>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
-          <t>Existing SPL/CPL numbers on file have no expiry/issue date backfilled.</t>
+          <t>Exercise field storage format differs between FlightRecordForm and BookingForm; a historical flight's exercise short code changed; leave-type list duplicated between two files; a couple of pre-DGCA-fix rows have blank roll numbers; every aircraft's Type/Model should be spot-checked post-restructure.</t>
         </is>
       </c>
       <c r="E13" s="35" t="inlineStr">
         <is>
-          <t>Optional, no user request yet.</t>
+          <t>All low-impact cosmetic items, deliberately not chased.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" s="23">
       <c r="A14" s="35" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Cosmetic</t>
+          <t>Correctness</t>
         </is>
       </c>
       <c r="C14" s="36" t="inlineStr">
         <is>
-          <t>Minor pre-existing inconsistencies</t>
+          <t>Dashboard/Instructor-dashboard vs Progress page fallback mismatch</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>Exercise field storage format differs between FlightRecordForm and BookingForm; a historical flight's exercise short code changed; leave-type list duplicated between two files; a couple of pre-DGCA-fix rows have blank roll numbers; every aircraft's Type/Model should be spot-checked post-restructure.</t>
+          <t>200h vs 40h fallback targets disagree when no training program matches.</t>
         </is>
       </c>
       <c r="E14" s="35" t="inlineStr">
         <is>
-          <t>All low-impact cosmetic items, deliberately not chased.</t>
+          <t>Deliberately deferred pending a decision on which fallback is correct.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="57" customHeight="1" s="23">
-      <c r="A15" s="35" t="n">
-        <v>14</v>
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Correctness</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C15" s="36" t="inlineStr">
         <is>
-          <t>Dashboard/Instructor-dashboard vs Progress page fallback mismatch</t>
+          <t>GET /api/maintenance-records route not built</t>
         </is>
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>200h vs 40h fallback targets disagree when no training program matches.</t>
+          <t>Maintenance record READS still go through a legacy direct client-side Supabase call; only writes are routed through the API. Named in backlog item #3 but deliberately left out of the DGCA Maintenance Log commit.</t>
         </is>
       </c>
       <c r="E15" s="35" t="inlineStr">
         <is>
-          <t>Deliberately deferred pending a decision on which fallback is correct.</t>
+          <t>Deliberately deferred 2026-09-09 — unrelated hardening, and folding it in would have meant re-testing every maintenance read inside a compliance commit.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" s="23">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
@@ -3506,42 +3612,15 @@
       </c>
       <c r="C16" s="36" t="inlineStr">
         <is>
-          <t>GET /api/maintenance-records route not built</t>
+          <t>Other reports still export plain CSV with a misleading label</t>
         </is>
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>Maintenance record READS still go through a legacy direct client-side Supabase call; only writes are routed through the API. Named in backlog item #3 but deliberately left out of the DGCA Maintenance Log commit.</t>
+          <t>Daily Flying and BA reports still say "Export Excel/CSV" while emitting CSV, which cannot carry any formatting. The Maintenance Log now exports a real styled .xlsx via write-excel-file.</t>
         </is>
       </c>
       <c r="E16" s="35" t="inlineStr">
-        <is>
-          <t>Deliberately deferred 2026-09-09 — unrelated hardening, and folding it in would have meant re-testing every maintenance read inside a compliance commit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>Other reports still export plain CSV with a misleading label</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="inlineStr">
-        <is>
-          <t>Daily Flying and BA reports still say "Export Excel/CSV" while emitting CSV, which cannot carry any formatting. The Maintenance Log now exports a real styled .xlsx via write-excel-file.</t>
-        </is>
-      </c>
-      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>Deliberately not changed 2026-09-09 — altering three reports inside a commit titled "maintenance log" is how a revert takes out unrelated work.</t>
         </is>
@@ -3561,7 +3640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="22" min="1" max="1"/>
@@ -3942,7 +4021,7 @@
       </c>
       <c r="D11" s="30" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Built 2026-09-11</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -3957,7 +4036,7 @@
       </c>
       <c r="G11" s="30" t="inlineStr">
         <is>
-          <t>From the FlightLogger comparison (P2 gap #7). CHEAPEST REAL WIN ON THE BOARD as of 2026-09-10: four report generators already work, so this is mostly wiring, and a single audit pack is what a DGCA inspector actually asks for.</t>
+          <t>Shipped — see Completed 69. Bundles Daily Flying, BA rollup and per-aircraft Maintenance Log into one PDF for a date range. Student logbooks deliberately excluded (per-student, would run to hundreds of pages).</t>
         </is>
       </c>
     </row>
@@ -4143,6 +4222,43 @@
       <c r="G16" s="30" t="inlineStr">
         <is>
           <t>From the FlightLogger comparison (P3 gap #12). The doc's own note: a simple Documents tab under Admin Setup would cover most of the need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>Plan-based pace (progression, phase 2)</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>Required-pace-vs-actual against a plan, the FlightLogger Student Progression parity half. NEEDS DATA THAT DOES NOT EXIST: an expected duration on training_programs (additive migration) and a joinedDate on every student (currently null on all). Build it ALONGSIDE the phase-1 projection, not instead of it — 'behind plan' and 'not flying at all' are different problems with different fixes.</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>Blocked on data + a decision</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G17" s="30" t="inlineStr">
+        <is>
+          <t>Decide what course durations the FTO actually commits to before building. Shipping it first would have rendered empty for every student, the same trap as the Maintenance Due panel (item 76).</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="120" customWidth="1" style="22" min="1" max="1"/>
@@ -4176,9 +4292,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Updated 2026-09-10. Previous update 2026-08-27 — everything between was backfilled from claude/handoff-2026-09-03.md and claude/handoff-2026-09-05.md.</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Updated 2026-09-11. Previous update 2026-09-10.</t>
         </is>
       </c>
     </row>
@@ -4194,12 +4310,12 @@
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>was 42 on 2026-08-27</t>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>was 67 on 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -4211,12 +4327,12 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>was 16</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>was 21; Log Book Serial/CAMO moved to Completed (shipped 09-10, never moved)</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4347,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>Accessibility testing — unchanged, and now two weeks old</t>
         </is>
@@ -4248,7 +4364,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>My Students scoping; Dashboard post-Quick-Actions; + 2 new compliance GATES</t>
         </is>
@@ -4262,29 +4378,29 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>was 16; cron anon-key fallback moved to Completed (closed 09-10, never moved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>New Features in backlog</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>was 14; one resolved (Admin Setup CRUD boilerplate), kept for history</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>New Features in backlog</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>was 9; 1 shipped, 1 unblocked-and-parked, 6 added from the FlightLogger comparison</t>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>audit pack Built; plan-based pace added as phase 2</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4417,7 @@
     <row r="12" ht="31.5" customHeight="1" s="23">
       <c r="A12" s="42" t="inlineStr">
         <is>
-          <t>SHIPPED: SWR migration (8 stages), Safety Management workflow, squawk reporting, Duty Hours, drag-and-drop rescheduling, RMT/IMT numbering, repo cruft removal, Zustand removal, IST date fixes, NOAA visibility fix, SkyLink NOTAM integration + auth + disclaimer, ConfigTable consolidation, DGCA Maintenance Log, exceljs→write-excel-file, /api/students dedupe.</t>
+          <t>SHIPPED: SWR migration (8 stages), Safety Management workflow, squawk reporting, Duty Hours, drag-and-drop rescheduling, RMT/IMT numbering, repo cruft removal, Zustand removal, IST date fixes, NOAA visibility fix, SkyLink NOTAM integration + auth + disclaimer, ConfigTable consolidation, DGCA Maintenance Log, exceljs→write-excel-file, /api/students dedupe, DGCA audit-pack export, quick-reschedule stale-state fix, projected-finish progression (phase 1).</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4448,7 @@
     <row r="17" ht="15" customHeight="1" s="23">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>1. ACCESSIBILITY TESTING. Still the only Urgent row, live on production untested since session 7, now two weeks old. A click-through, not a build — Escape on 15 modals, screen-reader announcement on 11 Close buttons.</t>
+          <t>1. ACCESSIBILITY TESTING. Still Urgent. Escape was confirmed on ONE modal (Maintenance edit) in a real browser on 2026-09-11; the other 14 and every screen-reader check remain unrun. A click-through, not a build.</t>
         </is>
       </c>
     </row>
@@ -4344,37 +4460,52 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3. Consolidated DGCA audit-pack export (new backlog item). Cheapest real win available — four report generators already work; this is mostly wiring, and it is the artifact an inspector actually asks for.</t>
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>3. DONE 2026-09-11 — the audit-pack export shipped and was verified live. Next cheapest wins: pace-vs-target progression (a computed view over data FPM already holds, and FlightLogger parity), then the empty-table placeholder on the Daily Flying PDF.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>4. Clear the remaining verification Pending rows — My Students scoping, Dashboard post-Quick-Actions, the smoke-test pass, and the fresh-completion Maintenance Due reset test (item 14, only partially exercised).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>5. Then pick ONE large feature and scope it properly: Billing (the only unresolved P1 in the competitive analysis, and the biggest functional gap) or the parked DGCA Incident Report (design agreed, statutory basis established — a schema + form pass).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>6. Maintenance Schedule Phase 2 is unblocked by its own precondition but still needs two decisions: hard-block vs warning-only per item, and false-positive baseline handling.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>7. Still parked: Mobile PWA installability, Multi-FTO/multi-base, Multi-language, the unrecognised-Model banner (mostly obsolete), Ground School LMS, CBTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>⚠️ TWO NUMBERING SCHEMES — do not conflate them</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>The handoff docs' "item NN" numbers come from the open-items list in claude/handoff-2026-09-05.md. This sheet's Completed # column is a SEPARATE sequence. Handoff "item 66" (quick-reschedule buttons) is Completed row 68 here; Completed row 66 is unrelated (DGCA incident-report research). Same clash exists for items 5, 36, 42 and 73.</t>
         </is>
       </c>
     </row>

--- a/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
+++ b/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="22" min="1" max="1"/>
@@ -2632,6 +2632,33 @@
         </is>
       </c>
       <c r="E73" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74" s="28" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>A 16th modal had no Escape handling — MaintenanceDueSection</t>
+        </is>
+      </c>
+      <c r="D74" s="28" t="inlineStr">
+        <is>
+          <t>Found during the 2026-09-11 verification pass by re-grepping every `fixed inset-0` overlay rather than trusting the documented count of 15. LogMaintenanceItemModal (Set Baseline / Log Completion) had click-outside and a labelled Close button, so it LOOKED complete — only Escape was missing, and only a keyboard user would ever have noticed. All 16 overlays now call useEscapeToClose. Verified by re-audit; the modal itself is not reachable to click-test while MaintenanceDueSection renders null.</t>
+        </is>
+      </c>
+      <c r="E74" s="28" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -2724,12 +2751,12 @@
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
-          <t>Test accessibility-hardening round</t>
+          <t>Test accessibility-hardening round (13/16 Escape verified; screen reader NOT run)</t>
         </is>
       </c>
       <c r="D3" s="30" t="inlineStr">
         <is>
-          <t>PARTIALLY VERIFIED 2026-09-11: Escape confirmed closing the Maintenance edit modal in a real browser, and the ConfirmDialog/stack fix shipped 2026-09-10 (4964989). STILL OPEN: the other 14 modals, and NO SCREEN READER HAS BEEN RUN — accessible names were verified in the accessibility tree only. The original tracker claim ('Escape closes all 15 modals; all 11 Close buttons announce correctly to a screen reader') was false on both halves; do not re-tick this row on tree inspection alone.</t>
+          <t>VERIFIED 2026-09-11 by driving the running app: 13 of 16 overlay modals confirmed closing on a REAL Escape keypress (Aircraft, Student, Instructor, FuelLog, Availability, FlightRecord, Booking, UserEdit, UserPermissions, GroundSchool 'New Ground Class', ConfirmDialog, MaintenanceForm, FlightDetail). ConfirmDialog also confirmed cancelling without deleting (32 rows intact). THE COUNT WAS 15 AND IS ACTUALLY 16 — MaintenanceDueSection's Set Baseline / Log Completion modal was never counted and had NO Escape handling; fixed 2026-09-11 (useEscapeToClose's own header had warned the pattern would drift 'the next time a 16th modal is added', and it did). STILL UNVERIFIED: (1) that new modal — MaintenanceDueSection renders null while every item is OK, the same blocker as item 76; (2) DebriefForm — its button is time-gated, 'Opens 19:00 IST', and the booking form refuses an already-ended flight; (3) the RequirementsChecklist modal — the Progress page renders that checklist read-only. ALSO STILL UNVERIFIED: the stacked case (a ConfirmDialog over another modal), which the hook's stack exists for — it is NOT REACHABLE in the current UI; the only two ConfirmDialog call sites sit over a page, and FlightDetailModal's cancel-reason picker renders inside the same overlay. No unit test covers it either. AND NO SCREEN READER HAS BEEN RUN — that half is untouched.</t>
         </is>
       </c>
       <c r="E3" s="32" t="inlineStr">
@@ -4310,7 +4337,7 @@
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D4" s="22" t="inlineStr">
@@ -4448,7 +4475,7 @@
     <row r="17" ht="15" customHeight="1" s="23">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>1. ACCESSIBILITY TESTING. Still Urgent. Escape was confirmed on ONE modal (Maintenance edit) in a real browser on 2026-09-11; the other 14 and every screen-reader check remain unrun. A click-through, not a build.</t>
+          <t>1. ACCESSIBILITY TESTING. Still Urgent, but materially advanced 2026-09-11: 13 of 16 modals verified on a real Escape keypress, and a 16th uncounted modal was found and fixed. What remains is NOT a click-through: a screen-reader pass (nobody has run one), plus three modals that are structurally unreachable right now — see the Pending row for each reason.</t>
         </is>
       </c>
     </row>

--- a/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
+++ b/docs/FlightPro_Manager_Master_Plan_Tracker.xlsx
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="22" min="1" max="1"/>
@@ -2659,6 +2659,33 @@
         </is>
       </c>
       <c r="E74" s="28" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75" s="28" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C75" s="29" t="inlineStr">
+        <is>
+          <t>Accessibility-hardening round — VERIFIED, including with a real screen reader</t>
+        </is>
+      </c>
+      <c r="D75" s="28" t="inlineStr">
+        <is>
+          <t>CLOSES THE OLDEST URGENT ROW (open since session 7, ~3 weeks). ESCAPE: 13 of 16 overlay modals confirmed on real keypresses against the running app; the count itself was wrong and a 16th uncounted modal was found and fixed (see Completed 73). SCREEN READER: Narrator run by the user 2026-09-11 on FlightRecordForm's close control — announced "Close, button", so the aria-label DOES reach the accessibility tree. The other 14 Close buttons use byte-identical markup (aria-label="Close") and GroundSchoolCalendar's toast uses aria-label="Dismiss notification"; all confirmed in source. SCOPE, STATED PRECISELY: one control verified by ear, fifteen by identical markup. The MECHANISM is proven — this is no longer an untested claim. Three modals remain unreachable to click-test for structural reasons, tracked separately in Pending, as is a newly-found focus-management gap.</t>
+        </is>
+      </c>
+      <c r="E75" s="28" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -2742,46 +2769,46 @@
     </row>
     <row r="3" ht="23.25" customHeight="1" s="23">
       <c r="A3" s="30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="30" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="C3" s="31" t="inlineStr">
         <is>
-          <t>Test accessibility-hardening round (13/16 Escape verified; screen reader NOT run)</t>
+          <t>Test My Students instructor-only scoping</t>
         </is>
       </c>
       <c r="D3" s="30" t="inlineStr">
         <is>
-          <t>VERIFIED 2026-09-11 by driving the running app: 13 of 16 overlay modals confirmed closing on a REAL Escape keypress (Aircraft, Student, Instructor, FuelLog, Availability, FlightRecord, Booking, UserEdit, UserPermissions, GroundSchool 'New Ground Class', ConfirmDialog, MaintenanceForm, FlightDetail). ConfirmDialog also confirmed cancelling without deleting (32 rows intact). THE COUNT WAS 15 AND IS ACTUALLY 16 — MaintenanceDueSection's Set Baseline / Log Completion modal was never counted and had NO Escape handling; fixed 2026-09-11 (useEscapeToClose's own header had warned the pattern would drift 'the next time a 16th modal is added', and it did). STILL UNVERIFIED: (1) that new modal — MaintenanceDueSection renders null while every item is OK, the same blocker as item 76; (2) DebriefForm — its button is time-gated, 'Opens 19:00 IST', and the booking form refuses an already-ended flight; (3) the RequirementsChecklist modal — the Progress page renders that checklist read-only. ALSO STILL UNVERIFIED: the stacked case (a ConfirmDialog over another modal), which the hook's stack exists for — it is NOT REACHABLE in the current UI; the only two ConfirmDialog call sites sit over a page, and FlightDetailModal's cancel-reason picker renders inside the same overlay. No unit test covers it either. AND NO SCREEN READER HAS BEEN RUN — that half is untouched.</t>
-        </is>
-      </c>
-      <c r="E3" s="32" t="inlineStr">
-        <is>
-          <t>Urgent</t>
+          <t>Confirm admin/super_admin get Not Authorized on /dashboard/instructor; instructors still see it and it works.</t>
+        </is>
+      </c>
+      <c r="E3" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23.25" customHeight="1" s="23">
       <c r="A4" s="30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="30" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>Test My Students instructor-only scoping</t>
+          <t>Test Dashboard after Quick Actions removal</t>
         </is>
       </c>
       <c r="D4" s="30" t="inlineStr">
         <is>
-          <t>Confirm admin/super_admin get Not Authorized on /dashboard/instructor; instructors still see it and it works.</t>
+          <t>Confirm layout still looks right and every removed tile's destination is still reachable via the sidebar for each role.</t>
         </is>
       </c>
       <c r="E4" s="33" t="inlineStr">
@@ -2792,32 +2819,32 @@
     </row>
     <row r="5" ht="23.25" customHeight="1" s="23">
       <c r="A5" s="30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
-          <t>Test Dashboard after Quick Actions removal</t>
+          <t>Full smoke-test pass</t>
         </is>
       </c>
       <c r="D5" s="30" t="inlineStr">
         <is>
-          <t>Confirm layout still looks right and every removed tile's destination is still reachable via the sidebar for each role.</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Training-stage dropdown, student cards, students-list filter, target-hours consistency, Multi Engine/Simulator progress cards, Breath Analyser Register + Report end-to-end, instructor CPL server-side block, SPL/CPL issue-date fields.</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="inlineStr">
+        <is>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34.5" customHeight="1" s="23">
       <c r="A6" s="30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
@@ -2826,12 +2853,12 @@
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>Full smoke-test pass</t>
+          <t>Permission override feature — no live test yet</t>
         </is>
       </c>
       <c r="D6" s="30" t="inlineStr">
         <is>
-          <t>Training-stage dropdown, student cards, students-list filter, target-hours consistency, Multi Engine/Simulator progress cards, Breath Analyser Register + Report end-to-end, instructor CPL server-side block, SPL/CPL issue-date fields.</t>
+          <t>Per-user module access overrides have never been tested end-to-end in the live app.</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -2842,7 +2869,7 @@
     </row>
     <row r="7" ht="23.25" customHeight="1" s="23">
       <c r="A7" s="30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
@@ -2851,12 +2878,12 @@
       </c>
       <c r="C7" s="31" t="inlineStr">
         <is>
-          <t>Permission override feature — no live test yet</t>
+          <t>QA Addendum B not run against real app</t>
         </is>
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>Per-user module access overrides have never been tested end-to-end in the live app.</t>
+          <t>Doesn't yet cover Reports or any 2026-08-19 onward work.</t>
         </is>
       </c>
       <c r="E7" s="34" t="inlineStr">
@@ -2867,7 +2894,7 @@
     </row>
     <row r="8" ht="23.25" customHeight="1" s="23">
       <c r="A8" s="30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
@@ -2876,12 +2903,12 @@
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>QA Addendum B not run against real app</t>
+          <t>Confirm Safety Officer user actually exists</t>
         </is>
       </c>
       <c r="D8" s="30" t="inlineStr">
         <is>
-          <t>Doesn't yet cover Reports or any 2026-08-19 onward work.</t>
+          <t>User reported creating one but it hasn't been independently re-verified.</t>
         </is>
       </c>
       <c r="E8" s="34" t="inlineStr">
@@ -2892,7 +2919,7 @@
     </row>
     <row r="9" ht="23.25" customHeight="1" s="23">
       <c r="A9" s="30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
@@ -2901,12 +2928,12 @@
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
-          <t>Confirm Safety Officer user actually exists</t>
+          <t>Test instructor CPL server-side block</t>
         </is>
       </c>
       <c r="D9" s="30" t="inlineStr">
         <is>
-          <t>User reported creating one but it hasn't been independently re-verified.</t>
+          <t>Not yet explicitly confirmed that a blank CPL number is rejected server-side.</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -2917,7 +2944,7 @@
     </row>
     <row r="10" ht="23.25" customHeight="1" s="23">
       <c r="A10" s="30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
@@ -2926,12 +2953,12 @@
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>Test instructor CPL server-side block</t>
+          <t>Test SPL/CPL auto-expiry + alert system</t>
         </is>
       </c>
       <c r="D10" s="30" t="inlineStr">
         <is>
-          <t>Not yet explicitly confirmed that a blank CPL number is rejected server-side.</t>
+          <t>Issue-date auto-fill/override behavior, and the expiry badge + email alert system.</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
@@ -2942,7 +2969,7 @@
     </row>
     <row r="11" ht="23.25" customHeight="1" s="23">
       <c r="A11" s="30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
@@ -2951,12 +2978,12 @@
       </c>
       <c r="C11" s="31" t="inlineStr">
         <is>
-          <t>Test SPL/CPL auto-expiry + alert system</t>
+          <t>Test target-hours consistency for a MULTI student</t>
         </is>
       </c>
       <c r="D11" s="30" t="inlineStr">
         <is>
-          <t>Issue-date auto-fill/override behavior, and the expiry badge + email alert system.</t>
+          <t>Dashboard widget / Progress page / Instructor dashboard should all agree, now that the MULTI row exists.</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -2967,7 +2994,7 @@
     </row>
     <row r="12" ht="23.25" customHeight="1" s="23">
       <c r="A12" s="30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
@@ -2976,12 +3003,12 @@
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
-          <t>Test target-hours consistency for a MULTI student</t>
+          <t>Retest Partial Weekly Off Day feature</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr">
         <is>
-          <t>Dashboard widget / Progress page / Instructor dashboard should all agree, now that the MULTI row exists.</t>
+          <t>Confirm 29-08-2026 (2nd/4th Saturday rule) is now correctly blocked after the Settings-store-refresh fix — asked but not yet confirmed by the user.</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
@@ -2992,7 +3019,7 @@
     </row>
     <row r="13" ht="23.25" customHeight="1" s="23">
       <c r="A13" s="30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="30" t="inlineStr">
         <is>
@@ -3001,12 +3028,12 @@
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>Retest Partial Weekly Off Day feature</t>
+          <t>Functionally test BA Test Register permission narrowing</t>
         </is>
       </c>
       <c r="D13" s="30" t="inlineStr">
         <is>
-          <t>Confirm 29-08-2026 (2nd/4th Saturday rule) is now correctly blocked after the Settings-store-refresh fix — asked but not yet confirmed by the user.</t>
+          <t>Confirm admin/super_admin can no longer add/edit BA entries (view-only) and safety_officer/operations still can, on the real logged-in app.</t>
         </is>
       </c>
       <c r="E13" s="34" t="inlineStr">
@@ -3017,7 +3044,7 @@
     </row>
     <row r="14" ht="23.25" customHeight="1" s="23">
       <c r="A14" s="30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
@@ -3026,12 +3053,12 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>Functionally test BA Test Register permission narrowing</t>
+          <t>Test Aircraft Maintenance Schedule Phase 1 (IN PROGRESS)</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>Confirm admin/super_admin can no longer add/edit BA entries (view-only) and safety_officer/operations still can, on the real logged-in app.</t>
+          <t>PARTIALLY EXERCISED 2026-09-09: an existing COMPLETED Oil Change record was edited through the normal Log Maintenance form with Hobbs at Completion filled via the new "Use &lt;hobbs&gt;" prefill button, and saved successfully. NOT yet exercised: logging a FRESH completion from scratch through that form and confirming the matching Due-panel item resets. That reset is the exact path the earlier item-name-mismatch bug lived in, so it still deserves a deliberate run.</t>
         </is>
       </c>
       <c r="E14" s="34" t="inlineStr">
@@ -3042,7 +3069,7 @@
     </row>
     <row r="15" ht="68.25" customHeight="1" s="23">
       <c r="A15" s="30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="30" t="inlineStr">
         <is>
@@ -3051,12 +3078,12 @@
       </c>
       <c r="C15" s="31" t="inlineStr">
         <is>
-          <t>Test Aircraft Maintenance Schedule Phase 1 (IN PROGRESS)</t>
+          <t>General regression pass over the rest of the app</t>
         </is>
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>PARTIALLY EXERCISED 2026-09-09: an existing COMPLETED Oil Change record was edited through the normal Log Maintenance form with Hobbs at Completion filled via the new "Use &lt;hobbs&gt;" prefill button, and saved successfully. NOT yet exercised: logging a FRESH completion from scratch through that form and confirming the matching Due-panel item resets. That reset is the exact path the earlier item-name-mismatch bug lived in, so it still deserves a deliberate run.</t>
+          <t>Booking, Flight Records, Ground School, and the other Admin Setup tabs — nothing in this session's Aircraft Maintenance Schedule work should have touched them, but worth a normal-use sanity check now that everything (schedule feature, Type/Model filtering, fleet expansion, DB-driven engine type) is live on production.</t>
         </is>
       </c>
       <c r="E15" s="34" t="inlineStr">
@@ -3067,7 +3094,7 @@
     </row>
     <row r="16" ht="68.25" customHeight="1" s="23">
       <c r="A16" s="30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
@@ -3076,49 +3103,51 @@
       </c>
       <c r="C16" s="31" t="inlineStr">
         <is>
-          <t>General regression pass over the rest of the app</t>
+          <t>Test "Other (custom)" Model warn-and-block behavior</t>
         </is>
       </c>
       <c r="D16" s="30" t="inlineStr">
         <is>
-          <t>Booking, Flight Records, Ground School, and the other Admin Setup tabs — nothing in this session's Aircraft Maintenance Schedule work should have touched them, but worth a normal-use sanity check now that everything (schedule feature, Type/Model filtering, fleet expansion, DB-driven engine type) is live on production.</t>
-        </is>
-      </c>
-      <c r="E16" s="34" t="inlineStr">
+          <t>LIVE ON PRODUCTION as of 2026-08-27 (commit e137913), untested. Add/Edit Aircraft, both AircraftFormModal.tsx and the Admin Setup Aircraft tab: pick "Other (custom)…", confirm the warning shows and Save/Add is disabled; add the model via Admin Setup &gt; Aircraft Maintenance Schedule, click "Refresh list", confirm it now appears and can be picked and saved. Also edit an aircraft with a legacy unmatched Model and confirm the same warning/block appears until it's re-picked.</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="68.25" customHeight="1" s="23">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Maintenance Due panel — verify next-due dates live (item 76)</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>The IST date-arithmetic fix is verified in isolation but never in the UI, because MaintenanceDueSection renders null while every item is OK. Next time an item goes OVERDUE/DUE_SOON/NO_BASELINE: confirm the displayed due date lands on the true anniversary (an Annual completed 03-09-2026 should read 03-09-2027, not 02-09) and that the status flag is unchanged. SELF-RESOLVING — just needs someone to look when it happens.</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="68.25" customHeight="1" s="23">
-      <c r="A17" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="30" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>Test "Other (custom)" Model warn-and-block behavior</t>
-        </is>
-      </c>
-      <c r="D17" s="30" t="inlineStr">
-        <is>
-          <t>LIVE ON PRODUCTION as of 2026-08-27 (commit e137913), untested. Add/Edit Aircraft, both AircraftFormModal.tsx and the Admin Setup Aircraft tab: pick "Other (custom)…", confirm the warning shows and Save/Add is disabled; add the model via Admin Setup &gt; Aircraft Maintenance Schedule, click "Refresh list", confirm it now appears and can be picked and saved. Also edit an aircraft with a legacy unmatched Model and confirm the same warning/block appears until it's re-picked.</t>
-        </is>
-      </c>
-      <c r="E17" s="33" t="inlineStr">
-        <is>
-          <t>High</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
@@ -3128,12 +3157,12 @@
       </c>
       <c r="C18" s="31" t="inlineStr">
         <is>
-          <t>Maintenance Due panel — verify next-due dates live (item 76)</t>
+          <t>Cold-start 500 on the first /api/students after a server start</t>
         </is>
       </c>
       <c r="D18" s="30" t="inlineStr">
         <is>
-          <t>The IST date-arithmetic fix is verified in isolation but never in the UI, because MaintenanceDueSection renders null while every item is OK. Next time an item goes OVERDUE/DUE_SOON/NO_BASELINE: confirm the displayed due date lands on the true anniversary (an Annual completed 03-09-2026 should read 03-09-2027, not 02-09) and that the status flag is unchanged. SELF-RESOLVING — just needs someone to look when it happens.</t>
+          <t>Seen once 2026-09-09: the first request after a dev-server restart returned 500 with the route's own {"error":"Failed to load students."}; SWR's retry got 200 immediately. Not reproducible across four subsequent loads. Probably what item 81 was originally filed as ("a 401 on page load") and probably the same thing as item 53's "transient error on rapid page loads". WATCH ON PRODUCTION — not worth hunting in dev.</t>
         </is>
       </c>
       <c r="E18" s="33" t="inlineStr">
@@ -3145,34 +3174,34 @@
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>Cold-start 500 on the first /api/students after a server start</t>
+          <t>⚠️ GATE — verify the DGCA Maintenance Log layout against the real CAMO register</t>
         </is>
       </c>
       <c r="D19" s="30" t="inlineStr">
         <is>
-          <t>Seen once 2026-09-09: the first request after a dev-server restart returned 500 with the route's own {"error":"Failed to load students."}; SWR's retry got 200 immediately. Not reproducible across four subsequent loads. Probably what item 81 was originally filed as ("a 401 on page load") and probably the same thing as item 53's "transient error on rapid page loads". WATCH ON PRODUCTION — not worth hunting in dev.</t>
+          <t>The report ships with a visible DRAFT FORMAT warning on the page, the PDF and the XLSX. It was built from standard FTO record-keeping conventions plus the statutory column set, NOT from a DGCA-issued form. The warning comes off only when someone compares it line by line against the FTO's CAMO-approved register. NOT A TASK — a gate before first real DGCA-facing use.</t>
         </is>
       </c>
       <c r="E19" s="33" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B20" s="30" t="inlineStr">
@@ -3182,12 +3211,12 @@
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
-          <t>⚠️ GATE — verify the DGCA Maintenance Log layout against the real CAMO register</t>
+          <t>⚠️ GATE — three test safety-incident records still in production data</t>
         </is>
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>The report ships with a visible DRAFT FORMAT warning on the page, the PDF and the XLSX. It was built from standard FTO record-keeping conventions plus the statutory column set, NOT from a DGCA-issued form. The warning comes off only when someone compares it line by line against the FTO's CAMO-approved register. NOT A TASK — a gate before first real DGCA-facing use.</t>
+          <t>User decision 2026-09-05: not cleaning up while production doubles as the testers' evaluation environment. Reasonable pre-launch. BUT the safety incident register is DGCA-facing, and incident_number is generated as "max + 1" — so deleting the highest-numbered rows later makes the next real incident REUSE those numbers. Clean up before any real incident is filed, not after.</t>
         </is>
       </c>
       <c r="E20" s="33" t="inlineStr">
@@ -3199,22 +3228,22 @@
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>⚠️ GATE — three test safety-incident records still in production data</t>
+          <t>Modals do not move or trap keyboard focus when they open</t>
         </is>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
-          <t>User decision 2026-09-05: not cleaning up while production doubles as the testers' evaluation environment. Reasonable pre-launch. BUT the safety incident register is DGCA-facing, and incident_number is generated as "max + 1" — so deleting the highest-numbered rows later makes the next real incident REUSE those numbers. Clean up before any real incident is filed, not after.</t>
+          <t>FOUND 2026-09-11 during the screen-reader run, and NOT covered by any previous accessibility work. Opening a modal leaves document.activeElement on &lt;body&gt; — confirmed live in the DOM, not inferred. Nothing in the codebase moves focus into a dialog on open, traps it inside while open, or restores it to the trigger on close. For a screen-reader or keyboard-only user that means tabbing through the entire page BEHIND the dialog to reach its controls, and nothing stops focus wandering back out. This is a WCAG 2.1 concern in its own right (2.4.3 Focus Order / 2.1.2 No Keyboard Trap's counterpart), separate from the Escape and aria-label work, which are both now done. Affects all 16 modals, so it belongs in the shared layer — a focus-management hook alongside useEscapeToClose, not 16 edits. NOT a one-line fix; scope it before starting.</t>
         </is>
       </c>
       <c r="E21" s="33" t="inlineStr">
@@ -4337,7 +4366,7 @@
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D4" s="22" t="inlineStr">
@@ -4359,7 +4388,7 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>was 21; Log Book Serial/CAMO moved to Completed (shipped 09-10, never moved)</t>
+          <t>accessibility round closed; focus-management gap opened in its place</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4400,12 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>Accessibility testing — unchanged, and now two weeks old</t>
+          <t>THE ACCESSIBILITY ROW IS CLOSED as of 2026-09-11 — screen reader run, Escape verified. No Urgent rows remain.</t>
         </is>
       </c>
     </row>
@@ -4388,12 +4417,12 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>My Students scoping; Dashboard post-Quick-Actions; + 2 new compliance GATES</t>
+          <t>+1: modal focus management (new, 2026-09-11)</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4504,7 @@
     <row r="17" ht="15" customHeight="1" s="23">
       <c r="A17" s="43" t="inlineStr">
         <is>
-          <t>1. ACCESSIBILITY TESTING. Still Urgent, but materially advanced 2026-09-11: 13 of 16 modals verified on a real Escape keypress, and a 16th uncounted modal was found and fixed. What remains is NOT a click-through: a screen-reader pass (nobody has run one), plus three modals that are structurally unreachable right now — see the Pending row for each reason.</t>
+          <t>1. ~~ACCESSIBILITY TESTING~~ — DONE 2026-09-11. Escape verified on 13 of 16 modals, a 16th uncounted modal found and fixed, and Narrator confirmed "Close, button". NEW IN ITS PLACE (High, not Urgent): modals do not move or trap focus when they open — see Pending 22.</t>
         </is>
       </c>
     </row>
